--- a/Employee_Reports_wi48/Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage Q0568.xlsx
+++ b/Employee_Reports_wi48/Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage Q0568.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1426,9 +1426,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1440,11 +1452,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1489,11 +1501,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1526,11 +1538,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1563,11 +1575,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1612,11 +1624,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1649,11 +1661,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1686,11 +1698,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2241,7 +2253,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7943</v>
+        <v>7940</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2336,7 +2348,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2365,7 +2377,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2394,7 +2406,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2423,7 +2435,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2452,7 +2464,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2481,7 +2493,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2510,7 +2522,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
